--- a/03-screening/full-text-screening.xlsx
+++ b/03-screening/full-text-screening.xlsx
@@ -1506,6 +1506,7 @@
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="6" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="42.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
